--- a/CSharp/SpreadSheetAsData.CodeGenerationのテスト/TestData/コード生成/文脈付き名前置換.xlsx
+++ b/CSharp/SpreadSheetAsData.CodeGenerationのテスト/TestData/コード生成/文脈付き名前置換.xlsx
@@ -8,6 +8,7 @@
   </x:sheets>
   <x:definedNames>
     <x:definedName name="total">sales_data!$B$2</x:definedName>
+    <definedName xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="total" localSheetId="2">sales_data!$B$2</definedName>
   </x:definedNames>
 </x:workbook>
 </file>
